--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.881</v>
+        <v>0.874</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>94.48999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.41</v>
+        <v>49.58</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.993</v>
+        <v>0.911</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.762</v>
+        <v>0.726</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04383999824523926</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>106978517.6123181</v>
+        <v>106978527.4707543</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>47.41</v>
+        <v>49.58</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5071851520</v>
+        <v>5303995392</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>22.68</v>
+        <v>23.72</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>12.85</v>
+        <v>12.49</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>8454407680</v>
+        <v>8550198784</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.357334</v>
+        <v>16.542667</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>10.999</v>
+        <v>11.164</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.295</v>
+        <v>2.329</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>7955880960</v>
+        <v>8132750336</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>35.855072</v>
+        <v>37.191177</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.78</v>
+        <v>11.672</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.195</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>10288844800</v>
+        <v>10292901888</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>23.925875</v>
+        <v>23.93531</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.201</v>
+        <v>15.717</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.726</v>
+        <v>2.819</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>9631537152</v>
+        <v>9230223360</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>27.705883</v>
+        <v>26.551472</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.145</v>
+        <v>14.5</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.254</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>17071917056</v>
+        <v>16630402048</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>90.342674</v>
+        <v>88.55799</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>33.849</v>
+        <v>35.078</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.127</v>
+        <v>4.277</v>
       </c>
     </row>
     <row r="11">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>9996020736</v>
+        <v>10001286144</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>16.512</v>
+        <v>16.521</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.321</v>
+        <v>3.323</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>15220633600</v>
+        <v>14409650176</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>53.049305</v>
+        <v>50.45688</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>15.856</v>
+        <v>16.324</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>3.174</v>
+        <v>3.268</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>12287913984</v>
+        <v>12248612864</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>47.01916</v>
+        <v>46.77916</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>25.124</v>
+        <v>25.869</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.276</v>
+        <v>5.432</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.874</v>
+        <v>0.843</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>49.58</v>
+        <v>50.94</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.911</v>
+        <v>0.86</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.726</v>
+        <v>0.704</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>0.822</v>
+        <v>0.756</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04372</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>106978527.4707543</v>
+        <v>106978520.2983903</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>49.58</v>
+        <v>50.94</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5303995392</v>
+        <v>5449485824</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>23.72</v>
+        <v>24.37</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>12.49</v>
+        <v>13.28</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>8550198784</v>
+        <v>8506782720</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.542667</v>
+        <v>16.458668</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.164</v>
+        <v>11.266</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>2.329</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -1568,16 +1568,16 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>8132750336</v>
+        <v>8200281600</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>37.191177</v>
+        <v>37.5</v>
       </c>
       <c r="E7" s="34" t="n">
-        <v>11.672</v>
+        <v>11.974</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>2.175</v>
+        <v>2.231</v>
       </c>
     </row>
     <row r="8">
@@ -1592,16 +1592,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>10292901888</v>
+        <v>10260446208</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>23.93531</v>
+        <v>23.859837</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.717</v>
+        <v>15.617</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.819</v>
+        <v>2.801</v>
       </c>
     </row>
     <row r="9">
@@ -1616,16 +1616,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>9230223360</v>
+        <v>9273677824</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>26.551472</v>
+        <v>26.67647</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>14.5</v>
+        <v>14.081</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>2.31</v>
+        <v>2.244</v>
       </c>
     </row>
     <row r="10">
@@ -1640,16 +1640,16 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>16630402048</v>
+        <v>16401991680</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>88.55799</v>
+        <v>87.06874999999999</v>
       </c>
       <c r="E10" s="34" t="n">
-        <v>35.078</v>
+        <v>33.232</v>
       </c>
       <c r="F10" s="34" t="n">
-        <v>4.277</v>
+        <v>4.052</v>
       </c>
     </row>
     <row r="11">
@@ -1664,14 +1664,14 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>10001286144</v>
+        <v>9980702720</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
-        <v>16.521</v>
+        <v>16.501</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.323</v>
+        <v>3.319</v>
       </c>
     </row>
     <row r="12">
@@ -1686,16 +1686,16 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>14409650176</v>
+        <v>14628663296</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.45688</v>
+        <v>50.98608</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>16.324</v>
+        <v>15.912</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>3.268</v>
+        <v>3.186</v>
       </c>
     </row>
     <row r="13">
@@ -1710,16 +1710,16 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>12248612864</v>
+        <v>11608534016</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>46.77916</v>
+        <v>44.25</v>
       </c>
       <c r="E13" s="34" t="n">
-        <v>25.869</v>
+        <v>24.581</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>5.432</v>
+        <v>5.162</v>
       </c>
     </row>
     <row r="15">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="36" t="n">
         <v>0.333</v>

--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-27 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372</v>
+        <v>0.04372000217437744</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/PSN_research.xlsx
+++ b/app/reports/PSN_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-29 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.843</v>
+        <v>0.844</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>94.76000000000001</v>
+        <v>94.67</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>50.94</v>
+        <v>50.71</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>0.86</v>
+        <v>0.867</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.704</v>
+        <v>0.708</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04372000217437744</v>
+        <v>0.04375999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>106978520.2983903</v>
+        <v>106978517.8465786</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>50.94</v>
+        <v>50.71</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5449485824</v>
+        <v>5424880640</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>24.37</v>
+        <v>24.26</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>13.28</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>8506782720</v>
+        <v>8463366656</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>16.458668</v>
+        <v>16.374666</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>11.266</v>
@@ -1568,10 +1568,10 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>8200281600</v>
+        <v>8107023360</v>
       </c>
       <c r="D7" s="34" t="n">
-        <v>37.5</v>
+        <v>37.07353</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>11.974</v>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>10260446208</v>
+        <v>10109762560</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>23.859837</v>
+        <v>23.509434</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>15.617</v>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>9273677824</v>
+        <v>9419377664</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>26.67647</v>
+        <v>27.095587</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>14.081</v>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>16401991680</v>
+        <v>16423772160</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>87.06874999999999</v>
+        <v>87.18437</v>
       </c>
       <c r="E10" s="34" t="n">
         <v>33.232</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>9980702720</v>
+        <v>9999131648</v>
       </c>
       <c r="D11" s="34" t="n"/>
       <c r="E11" s="34" t="n">
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>14628663296</v>
+        <v>14584727552</v>
       </c>
       <c r="D12" s="34" t="n">
-        <v>50.98608</v>
+        <v>50.832947</v>
       </c>
       <c r="E12" s="34" t="n">
         <v>15.912</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>11608534016</v>
+        <v>11851348992</v>
       </c>
       <c r="D13" s="34" t="n">
-        <v>44.25</v>
+        <v>45.175575</v>
       </c>
       <c r="E13" s="34" t="n">
         <v>24.581</v>
